--- a/cucumber-for-appian/src/test/resources/testdata/End2End/03_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/03_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="107">
   <si>
     <t>TC ID</t>
   </si>
@@ -303,6 +303,51 @@
   </si>
   <si>
     <t>REQ-731</t>
+  </si>
+  <si>
+    <t>CYP806</t>
+  </si>
+  <si>
+    <t>TESLA MODEL Y</t>
+  </si>
+  <si>
+    <t>11 Jun 2027</t>
+  </si>
+  <si>
+    <t>8025</t>
+  </si>
+  <si>
+    <t>Neeti</t>
+  </si>
+  <si>
+    <t>Tripathi</t>
+  </si>
+  <si>
+    <t>03 Jul 1993</t>
+  </si>
+  <si>
+    <t>0499656877</t>
+  </si>
+  <si>
+    <t>neeti.tripathi@kmart.com.au.test</t>
+  </si>
+  <si>
+    <t>Kmart Australia Limited</t>
+  </si>
+  <si>
+    <t>27 Jul 2026</t>
+  </si>
+  <si>
+    <t>REQ-121</t>
+  </si>
+  <si>
+    <t>8065</t>
+  </si>
+  <si>
+    <t>29 Jul 2026</t>
+  </si>
+  <si>
+    <t>REQ-161</t>
   </si>
 </sst>
 </file>
@@ -1464,15 +1509,15 @@
         <v>38</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D2" s="6" t="n">
         <f>C2+1</f>
-        <v>5220.0</v>
+        <v>8066.0</v>
       </c>
       <c r="E2" s="6" t="n">
         <f>D2</f>
-        <v>5220.0</v>
+        <v>8066.0</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>40</v>
@@ -1514,17 +1559,17 @@
         <v>42</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>5,220 km</v>
+        <v>8,066 km</v>
       </c>
       <c r="W2" s="7" t="s">
         <v>47</v>
@@ -1533,41 +1578,43 @@
         <v>48</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="Z2" s="7" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="AA2" s="7" t="str">
         <f>_xlfn.CONCAT(Y2," ",Z2)</f>
-        <v>David Stewart</v>
+        <v>Neeti Tripathi</v>
       </c>
       <c r="AB2" s="7" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="AE2" s="7" t="s">
         <v>54</v>
       </c>
       <c r="AF2" s="7" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="AG2" s="7" t="str">
         <f>AI2&amp;" - "&amp;AH2</f>
-        <v>VOLVO C40 - CPK418</v>
+        <v>TESLA MODEL Y - CYP806</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" s="7"/>
+        <v>93</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>94</v>
+      </c>
       <c r="AK2" s="7" t="s">
         <v>56</v>
       </c>

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/03_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/03_NovatedApp_End2End.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="139">
   <si>
     <t>TC ID</t>
   </si>
@@ -433,6 +433,27 @@
   </si>
   <si>
     <t>ORI-143-961-540-468</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,079 km</t>
+  </si>
+  <si>
+    <t>0469 000 111</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,200 km</t>
+  </si>
+  <si>
+    <t>ORI-255-412-330-173</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,203 km</t>
+  </si>
+  <si>
+    <t>ORI-588-203-898-404</t>
   </si>
 </sst>
 </file>
@@ -1033,24 +1054,24 @@
         <v>34</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>SUBSTITUTE(C2,"Latest Reading (kms)","")</f>
         <v xml:space="preserve">
-18,065 km</v>
+21,203 km</v>
       </c>
       <c r="E2" s="5" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(CLEAN(D2),"km",""),",","")," ",""),CHAR(160),"")</f>
-        <v>18065</v>
+        <v>21203</v>
       </c>
       <c r="F2" s="5" t="n">
         <f>E2+1</f>
-        <v>18066.0</v>
+        <v>21204.0</v>
       </c>
       <c r="G2" s="5" t="n">
         <f>F2</f>
-        <v>18066.0</v>
+        <v>21204.0</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>35</v>
@@ -1105,7 +1126,7 @@
       </c>
       <c r="Y2" s="6" t="str">
         <f>TEXT(G2,"#,##0")&amp;" km"</f>
-        <v>18,066 km</v>
+        <v>21,204 km</v>
       </c>
       <c r="Z2" s="6" t="s">
         <v>38</v>
@@ -1127,7 +1148,7 @@
         <v>87</v>
       </c>
       <c r="AF2" s="6" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="AG2" s="6" t="s">
         <v>89</v>
@@ -1338,7 +1359,7 @@
         <v>118</v>
       </c>
       <c r="AV3" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="AW3" s="4" t="s">
         <v>120</v>
